--- a/LISTAS/mi/FRATACHO PINO.xlsx
+++ b/LISTAS/mi/FRATACHO PINO.xlsx
@@ -745,14 +745,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45163.60880736673</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="24">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -798,26 +794,6 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="24">
       <c r="A32" s="13" t="inlineStr">
         <is>
@@ -849,7 +825,7 @@
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>245.03</v>
+        <v>260</v>
       </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="16" t="n"/>
@@ -867,7 +843,7 @@
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="17" t="n">
-        <v>278.2</v>
+        <v>296.4</v>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="16" t="n"/>
@@ -885,7 +861,7 @@
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="17" t="n">
-        <v>301.847</v>
+        <v>321.1</v>
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="16" t="n"/>
@@ -903,7 +879,7 @@
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="17" t="n">
-        <v>328.49</v>
+        <v>351</v>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="16" t="n"/>
@@ -920,10 +896,8 @@
         </is>
       </c>
       <c r="C37" s="21" t="n"/>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D37" s="15" t="n">
+        <v>195.902</v>
       </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="16" t="n"/>
@@ -940,10 +914,8 @@
         </is>
       </c>
       <c r="C38" s="21" t="n"/>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D38" s="17" t="n">
+        <v>220.756</v>
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="16" t="n"/>
@@ -960,10 +932,8 @@
         </is>
       </c>
       <c r="C39" s="21" t="n"/>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D39" s="17" t="n">
+        <v>266.077</v>
       </c>
       <c r="F39" s="16" t="n"/>
     </row>
@@ -979,14 +949,11 @@
         </is>
       </c>
       <c r="C40" s="21" t="n"/>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D40" s="17" t="n">
+        <v>346.484</v>
       </c>
       <c r="F40" s="16" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="24">
       <c r="A42" s="12" t="inlineStr">
         <is>
@@ -994,16 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="24">
       <c r="A53" s="4" t="n"/>
     </row>
@@ -1012,19 +969,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/FRATACHO PINO.xlsx
+++ b/LISTAS/mi/FRATACHO PINO.xlsx
@@ -745,7 +745,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/mi/FRATACHO PINO.xlsx
+++ b/LISTAS/mi/FRATACHO PINO.xlsx
@@ -745,7 +745,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/mi/FRATACHO PINO.xlsx
+++ b/LISTAS/mi/FRATACHO PINO.xlsx
@@ -745,10 +745,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45266</v>
+        <v>45225.50784040913</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="24">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -794,6 +798,26 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="24">
       <c r="A32" s="13" t="inlineStr">
         <is>
@@ -825,7 +849,7 @@
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="16" t="n"/>
@@ -843,7 +867,7 @@
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="17" t="n">
-        <v>296.4</v>
+        <v>326.04</v>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="16" t="n"/>
@@ -861,7 +885,7 @@
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="17" t="n">
-        <v>321.1</v>
+        <v>353.22</v>
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="16" t="n"/>
@@ -879,7 +903,7 @@
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="17" t="n">
-        <v>351</v>
+        <v>386.2</v>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="16" t="n"/>
@@ -896,8 +920,10 @@
         </is>
       </c>
       <c r="C37" s="21" t="n"/>
-      <c r="D37" s="15" t="n">
-        <v>195.902</v>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="16" t="n"/>
@@ -914,8 +940,10 @@
         </is>
       </c>
       <c r="C38" s="21" t="n"/>
-      <c r="D38" s="17" t="n">
-        <v>220.756</v>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="16" t="n"/>
@@ -932,8 +960,10 @@
         </is>
       </c>
       <c r="C39" s="21" t="n"/>
-      <c r="D39" s="17" t="n">
-        <v>266.077</v>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" s="16" t="n"/>
     </row>
@@ -949,11 +979,14 @@
         </is>
       </c>
       <c r="C40" s="21" t="n"/>
-      <c r="D40" s="17" t="n">
-        <v>346.484</v>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F40" s="16" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="24">
       <c r="A42" s="12" t="inlineStr">
         <is>
@@ -961,6 +994,16 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="24">
       <c r="A53" s="4" t="n"/>
     </row>
@@ -969,19 +1012,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/FRATACHO PINO.xlsx
+++ b/LISTAS/mi/FRATACHO PINO.xlsx
@@ -745,14 +745,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45225.50784040913</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="24">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -798,26 +794,6 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="24">
       <c r="A32" s="13" t="inlineStr">
         <is>
@@ -849,7 +825,7 @@
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="16" t="n"/>
@@ -867,7 +843,7 @@
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="17" t="n">
-        <v>326.04</v>
+        <v>296.4</v>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="16" t="n"/>
@@ -885,7 +861,7 @@
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="17" t="n">
-        <v>353.22</v>
+        <v>321.1</v>
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="16" t="n"/>
@@ -903,7 +879,7 @@
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="17" t="n">
-        <v>386.2</v>
+        <v>351</v>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="16" t="n"/>
@@ -922,7 +898,7 @@
       <c r="C37" s="21" t="n"/>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>********</t>
         </is>
       </c>
       <c r="E37" s="3" t="n"/>
@@ -942,7 +918,7 @@
       <c r="C38" s="21" t="n"/>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>********</t>
         </is>
       </c>
       <c r="E38" s="3" t="n"/>
@@ -962,7 +938,7 @@
       <c r="C39" s="21" t="n"/>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>********</t>
         </is>
       </c>
       <c r="F39" s="16" t="n"/>
@@ -981,12 +957,11 @@
       <c r="C40" s="21" t="n"/>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>********</t>
         </is>
       </c>
       <c r="F40" s="16" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="24">
       <c r="A42" s="12" t="inlineStr">
         <is>
@@ -994,16 +969,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="24">
       <c r="A53" s="4" t="n"/>
     </row>
@@ -1012,18 +977,18 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
